--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -989,7 +989,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ dùng invariant input, chưa dùng search/route feasibility.</t>
+          <t>Dữ liệu đầu vào vi phạm tính toàn vẹn phải bị loại ngay trước khi chạy thuật toán routing: (a) Thông số vận tốc dùng chung bị xung đột giữa các dòng (0,8 vs 1,0), (b) trùng lặp order_id trong cùng một instance, (c) giá trị nhu cầu không phải là số hợp lệ ('abc').</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -1055,7 +1059,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính distance trước rồi chia đúng unit km/phút.</t>
+          <t>Khoảng cách Euclidean từ depot (0,0) tới order (3,4): sqrt(3^2 + 4^2) = sqrt(9 + 16) = 5 km. Thời gian di chuyển với vận tốc 0,5 km/phút: 5 km / 0,5 km/phút = 10 phút.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1145,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -1155,7 +1163,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Departure A không bằng arrival A khi có wait/service.</t>
+          <t>Arrival tại A = 4; Ready time A = 10; Service time = 3; Leg A-&gt;B = 2. Do xe đến trước ready time nên phải chờ đến t=10 mới bắt đầu service. Service hoàn tất lúc 10 + 3 = 13. Thời điểm arrival tại B = 13 + 2 = 15.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1181,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1187,7 +1199,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp max(0, arrival−due) cho từng order rồi cộng.</t>
+          <t>Lateness từng order: Order A = max(0, 12 - 10) = 2; Order B = max(0, 8 - 9) = 0; Order C = max(0, 20 - 14) = 6. Tổng lateness = 2 + 0 + 6 = 8 phút.</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1217,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
@@ -1219,7 +1235,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính max(0,arrival−due) từng order rồi lấy max.</t>
+          <t>Lateness của 4 orders: Order 1: max(0, 9-10)=0; Order 2: max(0, 15-11)=4; Order 3: max(0, 22-18)=4; Order 4: max(0, 30-31)=0. Maximum lateness = max(0, 4, 4, 0) = 4 phút.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1253,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -1251,7 +1271,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Overtime chỉ biết sau khi cộng return leg.</t>
+          <t>Hoàn tất service đơn cuối tại t=52; quay về depot mất 11 phút =&gt; Xe về tới depot lúc 52 + 11 = 63. Shift end = 60 =&gt; Overtime = max(0, 63 - 60) = 3 phút.</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1289,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -1283,7 +1307,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng bắt đầu return leg từ arrival trước service.</t>
+          <t>Đơn cuối arrival lúc t=40, service 8 phút =&gt; Hoàn tất lúc 40 + 8 = 48. Chặng về depot mất 7 phút =&gt; Về depot lúc 48 + 7 = 55. Shift end = 52 =&gt; Overtime = max(0, 55 - 52) = 3 phút.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -624,10 +624,32 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một artifact có thể support phần này nhưng không phần kia.
-Phân tích theo nguyên lý thiết kế: Một artifact có thể support phần này nhưng không phần kia.</t>
+- 1.0đ: Ánh xạ chuẩn xác phần tuyên bố Data Preparation được chứng minh 100% qua Git commits cá nhân.
+- 1.0đ: Bác bỏ phần tuyên bố Model Evaluation do hoàn toàn thiếu trace chứng minh vai trò cá nhân.
+- 1.0đ: Phân tích nguyên tắc cốt tử: sự tồn tại của artifact nhóm không tự động phân bổ công lao cá nhân.
+- 1.0đ: Soạn thảo lại bản tuyên bố đóng góp chuyên nghiệp, liêm chính, phản ánh chính xác sự thật có thể kiểm chứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Ánh xạ Tuyên bố Đóng góp Hồ sơ Năng lực (Portfolio Contribution Mapping) Dựa trên Bằng chứng Thực tế:
+1. **Bản đồ Bằng chứng Thực tế của Artifact Dự án Nhóm (Artifact Evidence Audit)**:
+- **Thành phần Artifact 1 (Jupyter Notebook nhóm trên Git)**:
+  + Lịch sử commit Git (`git log --author="Candidate"`) ghi nhận hàng chục commits độc lập cho các bước:     xử lý dữ liệu khuyết thiếu, chuẩn hóa định dạng văn bản, lọc nhiễu và xây dựng pipeline làm sạch dữ liệu.
+  + **Xác thực**: Có bằng chứng vật lý chứng minh 100% quyền sở hữu đóng góp cá nhân cho phần Data Cleaning/Preparation.
+- **Thành phần Artifact 2 (Báo cáo Cuối kỳ - Final Report)**:
+  + Báo cáo có biểu đồ và bảng kết quả đánh giá mô hình (Model Performance &amp; Evaluation Metrics).
+  + Tuy nhiên, trong toàn bộ kho lưu trữ Git và tài liệu đính kèm **HOÀN TOÀN KHÔNG CÓ TRACE LOG HAY COMMIT NÀO CHỨNG MINH AI LÀ NGƯỜI TRỰC TIẾP HUẤN LUYỆN VÀ ĐÁNH GIÁ MÔ HÌNH** (Zero individual trace for model training/eval).
+2. **Ánh xạ và Đánh giá Tính Hợp lệ của Tuyên bố (Claim Mapping &amp; Truthfulness Evaluation)**:
+- **Tuyên bố: 'Tôi phụ trách chuẩn bị dữ liệu (Data Preparation)'** -&gt; **HOÀN TOÀN ĐƯỢC CHẤP NHẬN (FULLY VERIFIED CLAIM)**. Được bảo chứng 100% bởi các commit cá nhân cụ thể trong repository.
+- **Tuyên bố: 'Tôi phụ trách đánh giá mô hình (Model Evaluation)'** -&gt; **BỊ BÁC BỎ / KHÔNG CÓ CĂN CỨ (UNSUPPORTED OVERCLAIM)**. Sự tồn tại của kết quả model trong bản báo cáo nhóm không tự động chứng minh bạn là người thực hiện. Tuyên bố này vi phạm tính liêm chính trong hồ sơ năng lực và sẽ bị đánh trượt ngay lập tức trong vòng phỏng vấn kỹ thuật khi nhà tuyển dụng yêu cầu mở git blame.
+3. **Viết lại Tuyên bố Đóng góp Chuẩn mực Đạt Chuẩn Liêm chính (Revised Professional Claim)**:
+```text
+'Trong dự án nhóm này, tôi là người trực tiếp xây dựng toàn bộ pipeline làm sạch và tiền xử lý dữ liệu 
+(chứng minh qua các commits trong notebook repo); đồng thời tôi tham gia thảo luận cùng nhóm 
+trong việc đối soát và trình bày kết quả đánh giá mô hình trên báo cáo tổng kết.'
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Minh bạch Đóng góp Cá nhân trong Dự án Nhóm (Contribution Attribution in Portfolio): Một artifact nhóm (Group Notebook/Report) có thể chứng minh năng lực của bạn ở phần này nhưng hoàn toàn không chứng minh ở phần khác. Nhà tuyển dụng công nghệ cao luôn sử dụng 'kỹ thuật phỏng vấn đào sâu' (Behavioral Deep-dive) chọc thẳng vào commit hash. Minh bạch nhận đúng phần việc mình làm và tôn trọng đóng góp của đồng đội là thước đo của sự trưởng thành nghề nghiệp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ACM Code of Ethics: Professional Responsibilities &amp; Tech Interview Best Practices for Portfolio Verification</t>
         </is>
       </c>
     </row>
@@ -710,10 +732,23 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cùng tiêu chí giúp alternative cạnh tranh công bằng.
-Phân tích theo nguyên lý thiết kế: Cùng tiêu chí giúp alternative cạnh tranh công bằng.</t>
+- 1.0đ: Thiết lập bảng so sánh hai nhánh nghề nghiệp trên các tiêu chí đánh giá chung công bằng, mạch lạc.
+- 1.0đ: Phân tích đúng thế mạnh của hồ sơ hiện tại đối với nhánh AI Application (RAG app, user workflow affinity).
+- 1.0đ: Chỉ rõ khoảng cách kỹ năng (gap) rất lớn và độ khó thu hẹp của nhánh AI Infrastructure (Linux, networking, GPU).
+- 1.0đ: Đưa ra khuyến nghị định hướng thực tế, khả thi dựa trên sự thật khách quan của thị trường tuyển dụng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Bảng So sánh Hai Nhánh Định hướng Nghề nghiệp (AI Application vs AI Infrastructure) trên Tiêu chí Chung:
+| Tiêu chí Đánh giá Chung | Nhánh A: AI Application Engineer (Kỹ sư Ứng dụng AI) | Nhánh B: AI Infrastructure Engineer (Kỹ sư Hạ tầng AI) |
+| :--- | :--- | :--- |
+| **1. Mức độ Khớp Năng lực Hiện tại (Skill &amp; Artifact Alignment)** | **RẤT CAO (ƯU THẾ TUYỆT ĐỐI)**: Ứng viên đã có sẵn sản phẩm RAG App hoàn chỉnh, am hiểu prompt orchestration, embeddings, và yêu thích tối ưu hóa luồng trải nghiệm người dùng (user workflow). | **THẤP / CÓ KHOẢNG TRỐNG LỚN (DEFICIT GAP)**: Hồ sơ hiện tại thiếu hụt nghiêm trọng kiến thức hạ tầng phân tán: Linux kernel, networking, CUDA internals, GPU memory management, Kubernetes operators. |
+| **2. Độ khó Thu hẹp Khoảng trống (Gap Closure Difficulty)** | **Thấp / Dễ dàng**: Chỉ cần bổ sung thêm kiến thức về kiểm chuẩn (Evaluation Frameworks: Ragas, LangSmith) và thiết kế API production trong 4-6 tuần. | **Rất cao / Kéo dài**: Đòi hỏi tối thiểu 6-12 tháng học tập chuyên sâu về hệ điều hành, mạng máy tính, distributed systems và phần cứng máy chủ. |
+| **3. Trọng tâm Công việc Hàng ngày (Day-to-Day Focus)** | Xây dựng tính năng cho người dùng cuối, cải thiện độ chính xác câu trả lời (groundedness), tích hợp công cụ (Tool calling/Agents), thiết kế UI/UX hội thoại. | Tối ưu hóa throughput suy luận mô hình (vLLM/Triton), quản lý cụm GPU, thiết lập mạng InfiniBand, duy trì tính ổn định của cụm phân tán và tối ưu hóa chi phí điện/phần cứng. |
+| **4. Cơ hội Tuyển dụng Ngắn hạn (Short-term Placement)** | **Rất Rộng mở**: Số lượng vị trí ứng dụng AI tại các doanh nghiệp và startup chiếm 80% nhu cầu thị trường hiện nay. | **Hẹp và Khắt khe**: Thường chỉ tuyển dụng tại các Cloud Vendor lớn hoặc phòng nghiên cứu AI, yêu cầu bằng cấp cao và kinh nghiệm hạ tầng dày dạn. |
+- **Khuyến nghị Quyết định Chiến lược**: Ứng viên nên chọn **Nhánh A: AI Application Engineer** làm trọng tâm mũi nhọn trước mắt để tận dụng tối đa thế mạnh sẵn có (RAG app, workflow affinity) nhằm có được việc làm ngay; đồng thời học bổ trợ dần dần các nguyên lý của Nhánh B để chuẩn bị cho bước tiến dài hạn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc So sánh Định hướng Nghề nghiệp trên Tiêu chí Chung (Common-Criteria Career Track Comparison): Khi đứng trước ngã rẽ sự nghiệp, việc so sánh cảm tính ('cái nào nghe ngầu hơn') luôn dẫn đến sai lầm. Bằng cách đặt hai nhánh AI Application và AI Infrastructure lên cùng một bàn cân tiêu chuẩn (Độ khớp hồ sơ, Khoảng cách kỹ năng, Trọng tâm công việc, Nhu cầu thị trường), ứng viên nhìn thấy rõ ràng: tận dụng đòn bẩy RAG app sẵn có vào nhánh Application là con đường có xác suất thành công cao nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Chip Huyen: AI Engineering (O'Reilly 2024) &amp; Latent Space: The Rise of the AI Engineer</t>
         </is>
       </c>
     </row>
@@ -744,10 +779,20 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu alternative không có điểm mạnh thật thì chưa phải steelman.
-Phân tích theo nguyên lý thiết kế: Nếu alternative không có điểm mạnh thật thì chưa phải steelman.</t>
+- 1.0 điểm: Nêu rõ quyết định chọn AI Infrastructure và dẫn chứng bằng chứng thực tế (debugging latency, dự án serving).
+- 1.0 điểm: Áp dụng phương pháp steelman trung thực cho alternative AI Application (ghi nhận lợi thế frontend và nhu cầu tuyển dụng).
+- 1.0 điểm: Phân tích đánh đổi sâu sắc, thừa nhận khoảng trống kỹ thuật và lý giải lợi thế hàng rào cạnh tranh dài hạn.
+- 1.0 điểm: Đưa ra kế hoạch hành động cụ thể và khả thi để thu hẹp khoảng trống Linux/networking trong 6 tháng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Decision Memo: Lựa chọn AI Infrastructure Track cho chu kỳ 6 tháng tới.
+1. Quyết định (Primary Track): Chọn AI Infrastructure làm hướng phát triển trọng tâm. Evidence hỗ trợ gồm sở thích và năng lực giải quyết bài toán độ trễ (latency debugging), kinh nghiệm thực hành tối ưu model serving (vLLM, TensorRT-LLM) và sự hứng thú với hệ thống phân tán.
+2. Steelman Alternative (AI Application): Thừa nhận trung thực phương án dự phòng AI Application có lợi thế cực kỳ mạnh mẽ: đã có sẵn kinh nghiệm frontend từ kỳ thực tập trước, thời gian ra mắt prototype nhanh, và thị trường tuyển dụng ứng dụng AI/RAG hiện tại rất rộng lớn.
+3. Rationale &amp; Trade-off: Lựa chọn Infra dù đối mặt khoảng trống kiến thức lớn về Linux kernel và networking (RDMA/eBPF). Lý do: AI Infra tạo ra rào cản kỹ thuật cao (high moat), giá trị lâu dài bền vững và ít bị thay thế bởi tooling tự động. Kỹ năng frontend sẵn có sẽ được tận dụng hiệu quả để xây dựng dashboard observability, internal profiling UI.
+4. Mitigation Plan: Hoàn thành khóa học Linux System Programming và Network Internals trong 8 tuần đầu; xây dựng 1 benchmark project đo lường TTFT/throughput đa GPU làm artifact cốt lõi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một decision memo tiêu chuẩn cần áp dụng kỹ thuật Steelman cho phương án thay thế, đối diện trực diện với các khoảng trống năng lực (Linux/networking) và chứng minh giá trị bền vững của con đường kỹ thuật đã chọn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Will Larson, Staff Engineer: Leadership beyond the management track, 'Architecture Decision Records &amp; Decision Memos', https://staffeng.com/guides/architecture-advice/</t>
         </is>
       </c>
     </row>
@@ -778,10 +823,21 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Memo phải sống được khi evidence hai phía xung đột.
-Phân tích theo nguyên lý thiết kế: Memo phải sống được khi evidence hai phía xung đột.</t>
+- 1.0 điểm: Đưa ra quyết định rõ ràng giải quyết mâu thuẫn giữa xu hướng thị trường và năng lực hiện có trong khung thời gian 4 tháng.
+- 1.0 điểm: Phân tích alternative hợp lý và có căn cứ logic chặt chẽ.
+- 1.0 điểm: Xác định tối thiểu 2 điểm bất định cốt lõi ảnh hưởng tới quyết định tuyển dụng.
+- 1.0 điểm: Thiết lập chiến lược phòng vệ rủi ro (hedging) cụ thể kết hợp cả hai khía cạnh.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Career Decision Memo: Xử lý xung đột giữa Bằng chứng Thị trường và Năng lực Cá nhân (Horizon 4 tháng).
+1. Bối cảnh xung đột: Dữ liệu tuyển dụng nghiêng mạnh về AI Infrastructure (nhu cầu GPU efficiency, cluster ops tăng cao), nhưng danh mục artifact thực tế và sở thích cá nhân lại thuộc về AI Application (RAG, agent workflow, full-stack prototypes); thời gian chuẩn bị cho kỳ internship chỉ còn 4 tháng.
+2. Quyết định (Decision): Tập trung toàn lực nộp hồ sơ vị trí AI Application Engineer cho kỳ thực tập 4 tháng tới. Lý do: Trong khung thời gian ngắn 4 tháng, xác suất nhận offer cao nhất khi ứng viên sở hữu artifact sẵn có chứng minh được kết quả ngay lập tức.
+3. Alternative: Tạm gác vị trí Pure Infra sang giai đoạn sau khi đã gia nhập doanh nghiệp, hoặc ứng tuyển hybrid (AI Platform).
+4. Key Uncertainties (Bất định): (a) Thị trường AI Application có thể bão hòa ứng viên junior; (b) Một số công ty Application yêu cầu tự host model open-source.
+5. Hedging Strategy: Tận dụng 4 tháng để nâng cấp artifact Application bằng cách tích hợp self-hosted backend (vLLM trên cloud instance), vừa làm dày hồ sơ Application vừa thể hiện tư duy hạ tầng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi bằng chứng thị trường và thế mạnh cá nhân xung đột trong khung thời gian ngắn, quyết định tối ưu là khai thác thế mạnh đã có artifact kiểm chứng để vượt qua vòng phỏng vấn, đồng thời quản trị các điểm bất định bằng chiến lược phòng vệ hybrid.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Gergely Orosz, The Pragmatic Engineer, 'Career Paths in Software Engineering and AI Transitions', https://newsletter.pragmaticengineer.com/</t>
         </is>
       </c>
     </row>
@@ -812,10 +868,25 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Trigger xem lại phải quan sát được, không phải cảm giác mơ hồ.
-Phân tích theo nguyên lý thiết kế: Trigger xem lại phải quan sát được, không phải cảm giác mơ hồ.</t>
+- 1.0 điểm: Phân kỳ timeline 6 tuần rõ ràng với các mục tiêu kỹ thuật cụ thể về Observability (OpenTelemetry, Prometheus, load test).
+- 1.0 điểm: Đặt cột mốc checkpoint tuần 3 với mentor gắn liền với sản phẩm kiểm chứng.
+- 1.0 điểm: Xây dựng ít nhất 2 trigger xem lại track hoàn toàn quan sát và đo lường được, không cảm tính.
+- 1.0 điểm: Nêu rõ kịch bản hành động chuyển hướng (reversal action) cụ thể khi trigger bị kích hoạt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kế hoạch Xây dựng Evidence 6 tuần cho AI Infrastructure với Trigger Reversible rõ ràng:
+1. Phân kỳ thực thi:
+- Tuần 1-2: Triển khai cụm serving LLM (vLLM/Triton), gắn OpenTelemetry instrumentation để thu thập TTFT, ITL, queue time và GPU kernel utilization vào Prometheus/Grafana.
+- Tuần 3 (Checkpoint Mentor): Trình bày kiến trúc telemetry và bài toán tối ưu bottleneck với mentor kỹ thuật.
+- Tuần 4-5: Thực hiện load testing đa luồng (k6/Locust), so sánh p95/p99 latency giữa các cấu hình speculative decoding hoặc batching.
+- Tuần 6: Đóng gói open-source repository hoàn chỉnh kèm technical postmortem và bài phân tích hiệu năng.
+2. Observable Reversal Triggers (Kích hoạt xem lại track tại Tuần 3):
+- Trigger 1: Nếu tại buổi review tuần 3, mentor đánh giá hiểu biết về Linux profiling (perf, eBPF, memory bandwidth) dưới chuẩn baseline và không thể giải thích cơ chế đo latency chuẩn xác.
+- Trigger 2: Nếu hệ thống observability không đo lường được các chỉ số GPU phần cứng ổn định do hạn chế môi trường và không tìm được giải pháp thay thế trước ngày thứ 21.
+3. Reversal Action: Nếu một trong hai trigger kích hoạt, pivot sang AI Application Track: tái sử dụng dashboard để làm giao diện phân tích chi phí người dùng, hoàn thành trong 3 tuần còn lại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một kế hoạch có tính thuận nghịch (reversible plan) phải xây dựng các điều kiện xem lại dựa trên các chỉ số quan sát định lượng hoặc đánh giá khách quan của chuyên gia, không phụ thuộc vào cảm giác nản lòng mơ hồ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jeff Bezos, Amazon Shareholder Letter (Type 1 and Type 2 Decisions / Reversibility), https://www.aboutamazon.com/news/company-news/2015-letter-to-shareholders</t>
         </is>
       </c>
     </row>
@@ -846,10 +917,25 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Reversible không có nghĩa thiếu commitment hiện tại.
-Phân tích theo nguyên lý thiết kế: Reversible không có nghĩa thiếu commitment hiện tại.</t>
+- 1.0 điểm: Lập kế hoạch 4 tuần chi tiết thể hiện cam kết mạnh mẽ vào evaluation và benchmark cho AI Agent.
+- 1.0 điểm: Thiết lập quy tắc kiểm tra kỹ thuật (Technical Benchmark Rule) đo lường được bằng tỷ lệ thành công/lỗi.
+- 1.0 điểm: Thiết lập quy tắc kiểm tra chuyên gia/thị trường (External Validation Rule) độc lập.
+- 1.0 điểm: Định hình rõ ràng con đường chuyển đổi (exit pathway) sang track kỹ thuật liên quan.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kế hoạch 4 tuần xây dựng AI Application Agent với Exit/Reconsideration Rules định lượng:
+1. Kế hoạch cam kết 100% trong 4 tuần:
+- Tuần 1: Thiết kế domain agent bài toán tài chính/hỗ trợ kỹ thuật; xây dựng evaluation benchmark suite gồm 60 test cases đa dạng có input, ground truth và strict criteria.
+- Tuần 2: Xây dựng pipeline đánh giá tự động (sử dụng deterministic code verifier kết hợp LLM-as-a-judge có rubric chi tiết, đo lường semantic accuracy, latency, chi phí token).
+- Tuần 3: Tối ưu agent loop (prompt refinement, tool schema, memory pruning) và chạy benchmark so sánh phiên bản.
+- Tuần 4: Viết benchmark evaluation report, đóng gói public repo với CI test tự động chạy evaluation suite.
+2. Quy tắc Thoát / Xem lại hướng đi (Exit Rules tại mốc 4 tuần):
+- Rule 1 (Technical Benchmark Fail): Nếu sau 4 tuần tối ưu, tỷ lệ hoàn thành tác vụ chính xác (Task Success Rate) của Agent đạt dưới 70% trên test suite chuẩn hoặc tỷ lệ tool hallucination &gt; 15%.
+- Rule 2 (Feedback/Moat Fail): Gửi artifact cho 2 senior engineers; nếu cả hai đều đánh giá artifact chỉ là wrapper API thông thường, không thể hiện được chiều sâu về stateful agent workflow hay evaluation rigour.
+3. Hành động khi Exit kích hoạt: Chuyển dịch ngay sang Data Engineering / MLOps track: sử dụng pipeline test và dữ liệu đã làm sạch để ứng tuyển các vị trí kỹ sư dữ liệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kế hoạch thuận nghịch đòi hỏi cam kết thực thi tối đa trong chu kỳ cam kết, đồng thời quy định các tiêu chí thoát khách quan về mặt kỹ thuật và phản hồi bên ngoài để kịp thời chuyển hướng mà không lãng phí tài nguyên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Annie Duke, 'Quit: The Power of Knowing When to Walk Away', Portfolio/Penguin, 2022.</t>
         </is>
       </c>
     </row>
@@ -932,10 +1018,26 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Grouping không được làm mất input-order contract.
-Phân tích theo nguyên lý thiết kế: Grouping không được làm mất input-order contract.</t>
+- 1.0 điểm: Mô tả chính xác cấu trúc dữ liệu gom nhóm (i2 chứa 2 đơn hàng, i1 và i3 mỗi bên chứa 1 đơn hàng).
+- 1.0 điểm: Khẳng định nguyên tắc bảo toàn thứ tự xuất hiện đầu tiên: thứ tự instance bắt buộc là [i2, i1, i3].
+- 1.0 điểm: Bảo đảm thứ tự xuất hiện của các order con bên trong từng instance (order ở row 1 trước row 3 của i2).
+- 1.0 điểm: Xác nhận cơ chế kiểm tra tính nhất quán của các trường chia sẻ dùng chung (shared fields) trong cùng một instance.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Mô tả Output Grouping và Thứ tự Instance cho dữ liệu CSV Routing:
+1. Cấu trúc Output Grouping:
+- Kết quả phân tích phải trả về cấu trúc ánh xạ có thứ tự (OrderedDict hoặc dictionary bảo toàn thứ tự chèn) gom nhóm toàn bộ các dòng theo từng instance_id duy nhất.
+- Instance i2: Gom 2 dòng đơn hàng (từ dòng xuất hiện đầu tiên row 1 và dòng row 3); các thông tin dùng chung (shared fields: depot coordinates, vehicle capacity) được kiểm tra nhất quán và lưu một lần ở cấp instance.
+- Instance i1: Chứa 1 dòng đơn hàng (từ row 2).
+- Instance i3: Chứa 1 dòng đơn hàng (từ row 4).
+2. Hợp đồng Thứ tự Instance (Instance Order Contract):
+- Thứ tự duyệt các instance trong output bắt buộc phải bảo toàn theo quy tắc 'xuất hiện lần đầu trong dữ liệu đầu vào' (first-seen input order): `[i2, i1, i3]`.
+- Không được tự ý sắp xếp lại theo alphabet `[i1, i2, i3]` hay thứ tự băm ngẫu nhiên của hash set, nhằm tránh làm sai lệch thứ tự xử lý của pipeline chấm điểm hạ nguồn.
+3. Thứ tự nội bộ các đơn hàng trong từng instance:
+- Các đơn hàng của instance i2 phải giữ nguyên thứ tự ban đầu: order từ dòng row 1 xếp trước order từ dòng row 3.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Grouping CSV cần bảo đảm hai nguyên tắc cốt lõi: gom đúng và đủ dữ liệu thuộc cùng một định danh thực thể, đồng thời tôn trọng hợp đồng bảo toàn thứ tự xuất hiện ban đầu (first-seen input order) của cả instance lẫn order con.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Python Software Foundation, 'collections.OrderedDict and dict insertion-order preservation guarantees', https://docs.python.org/3/library/collections.html</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1122,22 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Input repair cần authority riêng, không thuộc parser.
-Phân tích theo nguyên lý thiết kế: Input repair cần authority riêng, không thuộc parser.</t>
+- 1.0 điểm: Xác định chính xác lỗi vi phạm bất biến của trường chia sẻ depot_x mâu thuẫn giữa các dòng trong instance X.
+- 1.0 điểm: Nêu rõ hành vi validator: Fail-fast, từ chối nạp instance X và ghi nhận thông báo lỗi chi tiết.
+- 1.0 điểm: Khẳng định chính sách bất định: Tuyệt đối không tự ý suy đoán hoặc âm thầm sửa dữ liệu (no silent auto-repair).
+- 1.0 điểm: Phân biệt ranh giới kiến trúc giữa trách nhiệm của Parser (xác thực) và Data Repair Pipeline (sửa dữ liệu có kiểm toán).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân tích Validator Behavior và Uncertainty Policy cho Instance Invariant:
+1. Validator Behavior (Hành vi của bộ thẩm định):
+- Lỗi phát hiện: Vi phạm tính bất biến của thuộc tính dùng chung (Shared Instance Invariant Violation). Cụ thể, trường `depot_x` của instance X không đồng nhất giữa các dòng (hai dòng đầu có giá trị 0 hoặc 1, nhưng dòng thứ ba lại mang giá trị khác).
+- Hành vi xử lý: Validator phải áp dụng nguyên tắc Fail-Fast: từ chối toàn bộ instance X và ném ra ngoại lệ `InvariantValidationError` kèm thông tin ngữ cảnh chi tiết (tên instance, tên cột vi phạm, số dòng và các giá trị mâu thuẫn).
+2. Uncertainty Policy (Chính sách xử lý bất định):
+- Tuyệt đối cấm tự động sửa lỗi (No Silent Auto-Repair): Parser không được phép tự ý đoán giá trị depot bằng cách lấy giá trị dòng đầu, lấy giá trị trung bình hay đa số (majority vote). Vì vị trí depot ảnh hưởng trực tiếp đến ma trận khoảng cách; việc tự đoán sai sẽ phá hủy tính hợp lệ của toàn bộ bài toán tối ưu.
+- Phân định thẩm quyền kiến trúc (Architectural Authority): Parser chỉ có nhiệm vụ trích xuất cú pháp và xác thực bất biến. Quyền sửa đổi/làm sạch dữ liệu (Data Repair / Imputation Authority) phải thuộc về pipeline tiền xử lý dữ liệu độc lập có ghi nhận nhật ký kiểm toán (audit trail) rõ ràng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trường hợp dữ liệu chia sẻ của cùng một thực thể bị mâu thuẫn là lỗi vi phạm toàn vẹn cấu trúc nghiêm trọng. Parser phải từ chối ngay lập tức thay vì âm thầm suy đoán hay tự ý vá dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler, 'Fail Fast', IEEE Software, https://martinfowler.com/ieeeSoftware/failFast.pdf</t>
         </is>
       </c>
     </row>
@@ -1090,10 +1204,38 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Arrival được ghi trước waiting và service.
-Phân tích theo nguyên lý thiết kế: Arrival được ghi trước waiting và service.</t>
+- 1.0 điểm: Tính chính xác mốc Arrival at A = 5 và Waiting at A = 5.
+- 1.0 điểm: Tính chính xác Completion at A = 13 (bắt đầu phục vụ lúc 10 + 3).
+- 1.0 điểm: Tính chính xác Arrival at B = 17 và Waiting at B = 0.
+- 1.0 điểm: Tính chính xác Completion at B = 19, tuân thủ đúng thứ tự ghi nhận arrival trước waiting và service.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tính toán Trace Lan truyền Thời gian (Time Propagation Trace) tại A và B:
+1. Khởi hành tại Depot: t = 0.
+2. Chặng Depot -&gt; A:
+- Thời gian di chuyển (Leg travel time): 5 đơn vị.
+- Thời điểm đến (Arrival at A): t_arr(A) = 0 + 5 = 5.
+- Khung thời gian mở của A (Ready time): 10.
+- Vì t_arr(A) = 5 &lt; 10, xe đến sớm và phải chờ.
+- Thời gian chờ (Waiting at A): wait(A) = 10 - 5 = 5.
+- Thời điểm bắt đầu phục vụ (Start Service at A): t_start(A) = max(t_arr(A), ready(A)) = max(5, 10) = 10.
+- Thời gian phục vụ (Service time at A): 3.
+- Thời điểm hoàn thành (Completion at A): t_comp(A) = t_start(A) + service(A) = 10 + 3 = 13.
+3. Chặng A -&gt; B:
+- Rời A lúc t = 13. Thời gian di chuyển Leg A-&gt;B: 4 đơn vị.
+- Thời điểm đến (Arrival at B): t_arr(B) = 13 + 4 = 17.
+- Khung thời gian mở của B (Ready time): 0.
+- Vì t_arr(B) = 17 &gt;= 0, xe phục vụ ngay, không phải chờ.
+- Thời gian chờ (Waiting at B): wait(B) = max(0, 0 - 17) = 0.
+- Thời điểm bắt đầu phục vụ (Start Service at B): t_start(B) = max(17, 0) = 17.
+- Thời gian phục vụ (Service time at B): 2.
+- Thời điểm hoàn thành (Completion at B): t_comp(B) = 17 + 2 = 19.
+Tóm tắt kết quả theo chuẩn arrival -&gt; waiting -&gt; completion:
++ Stop A: Arrival = 5, Waiting = 5, Completion = 13.
++ Stop B: Arrival = 17, Waiting = 0, Completion = 19.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy tắc lan truyền thời gian trong VRPTW: Thời điểm đến (Arrival) được ghi nhận ngay khi kết thúc di chuyển; nếu đến trước ready time thì phát sinh waiting time; thời điểm hoàn thành bằng thời điểm bắt đầu phục vụ cộng service time.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Paolo Toth, Daniele Vigo, 'The Vehicle Routing Problem', SIAM Monographs on Discrete Mathematics and Applications, Section 3.2 Time Window Propagation.</t>
         </is>
       </c>
     </row>
@@ -1124,10 +1266,39 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ arrival trước service tại từng stop.
-Phân tích theo nguyên lý thiết kế: Giữ arrival trước service tại từng stop.</t>
+- 1.0 điểm: Tính toán chính xác toàn bộ mốc tại Stop A (Arrival = 3, Waiting = 2, Completion = 9).
+- 1.0 điểm: Tính toán chính xác toàn bộ mốc tại Stop B (Arrival = 11, Waiting = 4, Completion = 16).
+- 1.0 điểm: Tính toán chính xác toàn bộ mốc tại Stop C (Arrival = 19, Waiting = 0, Completion = 21).
+- 1.0 điểm: Duy trì tính liên tục và đúng quy tắc: Arrival ghi nhận trước Waiting và Service ở từng stop.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Trace Đầy đủ Lan truyền Thời gian qua 3 điểm dừng A, B, C:
+1. Khởi hành từ Depot lúc t = 0.
+2. Stop A (Depot -&gt; A):
+- Thời gian di chuyển: 3.
+- Arrival(A) = 0 + 3 = 3.
+- Ready time của A = 5 -&gt; Xe đến sớm, Waiting(A) = 5 - 3 = 2.
+- Start Service(A) = max(3, 5) = 5.
+- Service time = 4 -&gt; Completion(A) = 5 + 4 = 9.
+3. Stop B (A -&gt; B):
+- Rời A lúc t = 9. Thời gian di chuyển: 2.
+- Arrival(B) = 9 + 2 = 11.
+- Ready time của B = 15 -&gt; Xe đến sớm, Waiting(B) = 15 - 11 = 4.
+- Start Service(B) = max(11, 15) = 15.
+- Service time = 1 -&gt; Completion(B) = 15 + 1 = 16.
+4. Stop C (B -&gt; C):
+- Rời B lúc t = 16. Thời gian di chuyển: 3.
+- Arrival(C) = 16 + 3 = 19.
+- Ready time của C = 0 -&gt; Xe đến sau ready time, Waiting(C) = 0.
+- Start Service(C) = max(19, 0) = 19.
+- Service time = 2 -&gt; Completion(C) = 19 + 2 = 21.
+Bảng tổng kết 3 stop:
+- A: Arrival = 3, Waiting = 2, Start Service = 5, Completion = 9.
+- B: Arrival = 11, Waiting = 4, Start Service = 15, Completion = 16.
+- C: Arrival = 19, Waiting = 0, Start Service = 19, Completion = 21.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Lan truyền thời gian liên tục qua chuỗi các điểm dừng: thời điểm xuất phát từ trạm trước là mốc tính arrival trạm sau. Mỗi trạm phải ghi nhận độc lập: Arrival Time, Waiting Time, Service Start Time và Completion Time.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Olli Bräysy, Michel Gendreau, 'Vehicle Routing Problem with Time Windows, Part I: Route Construction and Local Search Algorithms', Transportation Science, 2005.</t>
         </is>
       </c>
     </row>
